--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -39,12 +39,12 @@
     <t xml:space="preserve">Arica</t>
   </si>
   <si>
+    <t xml:space="preserve">Camarones</t>
+  </si>
+  <si>
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
-    <t xml:space="preserve">Camarones</t>
-  </si>
-  <si>
     <t xml:space="preserve">General Lagos</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +504,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15201</v>
+        <v>15102</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3.06</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="4">
@@ -521,13 +521,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15102</v>
+        <v>15201</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-6.46</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-19.24</v>
+        <v>-20.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2.41</v>
+        <v>-24.08</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-5.89</v>
+        <v>-58.87</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-20.24</v>
+        <v>-202.42</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:34</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
